--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_25_9.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_25_9.xlsx
@@ -513,661 +513,661 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_25_9_0</t>
+          <t>model_25_9_24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9998824530055188</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7015941460871803</v>
       </c>
       <c r="D2" t="n">
-        <v>0.999974028462846</v>
+        <v>0.9997836254021666</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.9988160636364709</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.9995149998415385</v>
       </c>
       <c r="G2" t="n">
-        <v>0.125633654139209</v>
+        <v>6.978097368980307e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1771466053443431</v>
       </c>
       <c r="I2" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>0.0001374122273617272</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.0002979966555836046</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.0002177053844745614</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002709826989699447</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.008353500684731107</v>
       </c>
       <c r="N2" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000082974349046</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.008709126503010398</v>
       </c>
       <c r="P2" t="n">
-        <v>156.1487702277424</v>
+        <v>135.1402983371883</v>
       </c>
       <c r="Q2" t="n">
-        <v>248.7833329177256</v>
+        <v>205.8350961795439</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_25_9_22</t>
+          <t>model_25_9_23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9998835102908578</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7015761962796268</v>
       </c>
       <c r="D3" t="n">
-        <v>0.999974028462846</v>
+        <v>0.9997858807836394</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.9988266328683492</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.9995195617029342</v>
       </c>
       <c r="G3" t="n">
-        <v>0.125633654139209</v>
+        <v>6.915332344025065e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1771572611254982</v>
       </c>
       <c r="I3" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>0.0001359799104685395</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.0002953363810546435</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.0002156576701145453</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002705497668911136</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.0083158477282987</v>
       </c>
       <c r="N3" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000082228029983</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.008669870582270298</v>
       </c>
       <c r="P3" t="n">
-        <v>156.1487702277424</v>
+        <v>135.1583688793776</v>
       </c>
       <c r="Q3" t="n">
-        <v>248.7833329177256</v>
+        <v>205.8531667217333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_25_9_21</t>
+          <t>model_25_9_22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9998846618472772</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.701556282381388</v>
       </c>
       <c r="D4" t="n">
-        <v>0.999974028462846</v>
+        <v>0.999788348959105</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.9988382108095486</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.9995245526816577</v>
       </c>
       <c r="G4" t="n">
-        <v>0.125633654139209</v>
+        <v>6.846970980503548e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1771690828757284</v>
       </c>
       <c r="I4" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>0.0001344124552698256</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.0002924222144978401</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.0002134173348838328</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.00270067580101991</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.008274642578687945</v>
       </c>
       <c r="N4" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000081415166628</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.008626911244134195</v>
       </c>
       <c r="P4" t="n">
-        <v>156.1487702277424</v>
+        <v>135.1782382062386</v>
       </c>
       <c r="Q4" t="n">
-        <v>248.7833329177256</v>
+        <v>205.8730360485942</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_25_9_20</t>
+          <t>model_25_9_21</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9998859135519318</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7015341339071919</v>
       </c>
       <c r="D5" t="n">
-        <v>0.999974028462846</v>
+        <v>0.9997910669344373</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.9988508300053811</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.9995300123627289</v>
       </c>
       <c r="G5" t="n">
-        <v>0.125633654139209</v>
+        <v>6.772664385125142e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1771822311667755</v>
       </c>
       <c r="I5" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>0.0001326863605800592</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.000289245964261703</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.0002109666099800098</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002695368281713623</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.008229619909282044</v>
       </c>
       <c r="N5" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000080531610401</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.008579971866481913</v>
       </c>
       <c r="P5" t="n">
-        <v>156.1487702277424</v>
+        <v>135.2000617956879</v>
       </c>
       <c r="Q5" t="n">
-        <v>248.7833329177256</v>
+        <v>205.8948596380436</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_25_9_19</t>
+          <t>model_25_9_20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9998872745842016</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7015094129451938</v>
       </c>
       <c r="D6" t="n">
-        <v>0.999974028462846</v>
+        <v>0.9997940624960837</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.9988646042045783</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.9995359942249952</v>
       </c>
       <c r="G6" t="n">
-        <v>0.125633654139209</v>
+        <v>6.691867630234498e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1771969065977075</v>
       </c>
       <c r="I6" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>0.0001307839801612585</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.000285778999802638</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.0002082814899819482</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002689456151139107</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.0081803836280669</v>
       </c>
       <c r="N6" t="n">
-        <v>1.008671261181603</v>
+        <v>1.00007957088174</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.008528639494842286</v>
       </c>
       <c r="P6" t="n">
-        <v>156.1487702277424</v>
+        <v>135.224064924682</v>
       </c>
       <c r="Q6" t="n">
-        <v>248.7833329177256</v>
+        <v>205.9188627670376</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_25_9_18</t>
+          <t>model_25_9_19</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9998887491618492</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7014818892944408</v>
       </c>
       <c r="D7" t="n">
-        <v>0.999974028462846</v>
+        <v>0.9997973404854184</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.9988796309899888</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.9995425250536264</v>
       </c>
       <c r="G7" t="n">
-        <v>0.125633654139209</v>
+        <v>6.604330331225253e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1772132458257542</v>
       </c>
       <c r="I7" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>0.0001287022394197431</v>
       </c>
       <c r="J7" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.0002819967595282444</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.0002053499516447079</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002682879324012934</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.008126703102258168</v>
       </c>
       <c r="N7" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000078530003401</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.008472673677915868</v>
       </c>
       <c r="P7" t="n">
-        <v>156.1487702277424</v>
+        <v>135.2503998405855</v>
       </c>
       <c r="Q7" t="n">
-        <v>248.7833329177256</v>
+        <v>205.9451976829411</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_25_9_17</t>
+          <t>model_25_9_18</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9998903395594467</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7014512251391172</v>
       </c>
       <c r="D8" t="n">
-        <v>0.999974028462846</v>
+        <v>0.9998009473786109</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.99889590443308</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.9995496400825374</v>
       </c>
       <c r="G8" t="n">
-        <v>0.125633654139209</v>
+        <v>6.509917459679227e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1772314493929769</v>
       </c>
       <c r="I8" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>0.0001264116229037012</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.0002779007356494212</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.0002021561792765612</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002675479327607333</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.008068405951412725</v>
       </c>
       <c r="N8" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000077407369802</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.008411894696667196</v>
       </c>
       <c r="P8" t="n">
-        <v>156.1487702277424</v>
+        <v>135.2791973756697</v>
       </c>
       <c r="Q8" t="n">
-        <v>248.7833329177256</v>
+        <v>205.9739952180254</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_25_9_16</t>
+          <t>model_25_9_17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9998920457273368</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7014170151190717</v>
       </c>
       <c r="D9" t="n">
-        <v>0.999974028462846</v>
+        <v>0.9998048819932508</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.9989135124163974</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.9995573600925842</v>
       </c>
       <c r="G9" t="n">
-        <v>0.125633654139209</v>
+        <v>6.408631963461464e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1772517579386718</v>
       </c>
       <c r="I9" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>0.0001239128815223681</v>
       </c>
       <c r="J9" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.0002734688081389746</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.0001986908448306714</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002667377654225225</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.008005393159277977</v>
       </c>
       <c r="N9" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000076203015998</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.008346199319516811</v>
       </c>
       <c r="P9" t="n">
-        <v>156.1487702277424</v>
+        <v>135.3105592781046</v>
       </c>
       <c r="Q9" t="n">
-        <v>248.7833329177256</v>
+        <v>206.0053571204602</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_25_9_15</t>
+          <t>model_25_9_16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9998938656996907</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7013790268499109</v>
       </c>
       <c r="D10" t="n">
-        <v>0.999974028462846</v>
+        <v>0.9998091658833851</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.9989324740448526</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.9995657066946965</v>
       </c>
       <c r="G10" t="n">
-        <v>0.125633654139209</v>
+        <v>6.300590542664971e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1772743094162534</v>
       </c>
       <c r="I10" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>0.00012119232702558</v>
       </c>
       <c r="J10" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.0002686961682926599</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.00019494424765912</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002658291049955918</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007937625931388409</v>
       </c>
       <c r="N10" t="n">
-        <v>1.008671261181603</v>
+        <v>1.00007491832963</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.008275547100438482</v>
       </c>
       <c r="P10" t="n">
-        <v>156.1487702277424</v>
+        <v>135.3445641980697</v>
       </c>
       <c r="Q10" t="n">
-        <v>248.7833329177256</v>
+        <v>206.0393620404253</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_25_9_14</t>
+          <t>model_25_9_15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9998957973918134</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7013367007210054</v>
       </c>
       <c r="D11" t="n">
-        <v>0.999974028462846</v>
+        <v>0.9998138413664608</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.9989527837037385</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.9995747082498386</v>
       </c>
       <c r="G11" t="n">
-        <v>0.125633654139209</v>
+        <v>6.185916953784743e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1772994360347653</v>
       </c>
       <c r="I11" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>0.0001182230850264987</v>
       </c>
       <c r="J11" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.0002635842293316887</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.0001909036571790937</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002648298415654976</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007865060046677802</v>
       </c>
       <c r="N11" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000073554782249</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.008199891935783655</v>
       </c>
       <c r="P11" t="n">
-        <v>156.1487702277424</v>
+        <v>135.3813004313251</v>
       </c>
       <c r="Q11" t="n">
-        <v>248.7833329177256</v>
+        <v>206.0760982736807</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_25_9_13</t>
+          <t>model_25_9_14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9998978322101777</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7012895211643122</v>
       </c>
       <c r="D12" t="n">
-        <v>0.999974028462846</v>
+        <v>0.9998189110683896</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.9989744712008617</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.9995843749726701</v>
       </c>
       <c r="G12" t="n">
-        <v>0.125633654139209</v>
+        <v>6.065121345720542e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1773274438576691</v>
       </c>
       <c r="I12" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>0.0001150034878969127</v>
       </c>
       <c r="J12" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.0002581254886343142</v>
       </c>
       <c r="K12" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.0001865644882656134</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002637108397263524</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007787888896049135</v>
       </c>
       <c r="N12" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000072118439875</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.008119435449506421</v>
       </c>
       <c r="P12" t="n">
-        <v>156.1487702277424</v>
+        <v>135.4207418304719</v>
       </c>
       <c r="Q12" t="n">
-        <v>248.7833329177256</v>
+        <v>206.1155396728275</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_25_9_23</t>
+          <t>model_25_9_13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9998999548410216</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.701236841755305</v>
       </c>
       <c r="D13" t="n">
-        <v>0.999974028462846</v>
+        <v>0.9998244080509607</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.998997428816809</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.9995947000500374</v>
       </c>
       <c r="G13" t="n">
-        <v>0.125633654139209</v>
+        <v>5.939112809540658e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1773587166304877</v>
       </c>
       <c r="I13" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>0.0001115125392069089</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.000252347059165289</v>
       </c>
       <c r="K13" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.0001819297991860989</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002624660584894868</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007706563961676214</v>
       </c>
       <c r="N13" t="n">
-        <v>1.008671261181603</v>
+        <v>1.00007062011222</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.008034648344311422</v>
       </c>
       <c r="P13" t="n">
-        <v>156.1487702277424</v>
+        <v>135.462731402828</v>
       </c>
       <c r="Q13" t="n">
-        <v>248.7833329177256</v>
+        <v>206.1575292451836</v>
       </c>
     </row>
     <row r="14">
@@ -1177,712 +1177,712 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9999021426161586</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7011781119563359</v>
       </c>
       <c r="D14" t="n">
-        <v>0.999974028462846</v>
+        <v>0.999830344961613</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.9990215382568377</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.9996056584629874</v>
       </c>
       <c r="G14" t="n">
-        <v>0.125633654139209</v>
+        <v>5.809237026715083e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>1.374415341109035</v>
+        <v>0.177393581176151</v>
       </c>
       <c r="I14" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>0.0001077422069934587</v>
       </c>
       <c r="J14" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.0002462787156986301</v>
       </c>
       <c r="K14" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.0001770108203715483</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002610777056328322</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007621835098396634</v>
       </c>
       <c r="N14" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000069075800359</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.007946312397909104</v>
       </c>
       <c r="P14" t="n">
-        <v>156.1487702277424</v>
+        <v>135.5069524468656</v>
       </c>
       <c r="Q14" t="n">
-        <v>248.7833329177256</v>
+        <v>206.2017502892213</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_25_9_10</t>
+          <t>model_25_9_11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9999043612323102</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7011126514325285</v>
       </c>
       <c r="D15" t="n">
-        <v>0.999974028462846</v>
+        <v>0.9998367030693553</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.9990466385340573</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.9996171942255154</v>
       </c>
       <c r="G15" t="n">
-        <v>0.125633654139209</v>
+        <v>5.677530388029733e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1774324413708305</v>
       </c>
       <c r="I15" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>0.0001037043866789186</v>
       </c>
       <c r="J15" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.0002399609786174272</v>
       </c>
       <c r="K15" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.0001718326826481729</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002595421906841461</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007534938877011368</v>
       </c>
       <c r="N15" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000067509718369</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.007855716824479492</v>
       </c>
       <c r="P15" t="n">
-        <v>156.1487702277424</v>
+        <v>135.5528182352519</v>
       </c>
       <c r="Q15" t="n">
-        <v>248.7833329177256</v>
+        <v>206.2476160776075</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_25_9_9</t>
+          <t>model_25_9_10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9999065644979169</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7010396765172467</v>
       </c>
       <c r="D16" t="n">
-        <v>0.999974028462846</v>
+        <v>0.9998435053461736</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.9990723671937135</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.9996292195683084</v>
       </c>
       <c r="G16" t="n">
-        <v>0.125633654139209</v>
+        <v>5.54673502400452e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>1.374415341109035</v>
+        <v>0.177475762432894</v>
       </c>
       <c r="I16" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>9.93844895279483e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.0002334850777443925</v>
       </c>
       <c r="K16" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.0001664347836361704</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002578260760727156</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007447640582093446</v>
       </c>
       <c r="N16" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000065954472059</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.00776470206041453</v>
       </c>
       <c r="P16" t="n">
-        <v>156.1487702277424</v>
+        <v>135.5994319885639</v>
       </c>
       <c r="Q16" t="n">
-        <v>248.7833329177256</v>
+        <v>206.2942298309195</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_25_9_8</t>
+          <t>model_25_9_9</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9999086870075846</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7009582773700671</v>
       </c>
       <c r="D17" t="n">
-        <v>0.999974028462846</v>
+        <v>0.9998507197459285</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.9990983106953588</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.9996415966791394</v>
       </c>
       <c r="G17" t="n">
-        <v>0.125633654139209</v>
+        <v>5.420733681366485e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1775240844829199</v>
       </c>
       <c r="I17" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>9.480286696532373e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.0002269551011657551</v>
       </c>
       <c r="K17" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.0001608789840655394</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002559166078567337</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007362563195902963</v>
       </c>
       <c r="N17" t="n">
-        <v>1.008671261181603</v>
+        <v>1.00006445622994</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.00767600275375945</v>
       </c>
       <c r="P17" t="n">
-        <v>156.1487702277424</v>
+        <v>135.645388586228</v>
       </c>
       <c r="Q17" t="n">
-        <v>248.7833329177256</v>
+        <v>206.3401864285836</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_25_9_7</t>
+          <t>model_25_9_8</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9999106456943431</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7008675659744241</v>
       </c>
       <c r="D18" t="n">
-        <v>0.999974028462846</v>
+        <v>0.9998583225448611</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.9991238716225807</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.9996541406469196</v>
       </c>
       <c r="G18" t="n">
-        <v>0.125633654139209</v>
+        <v>5.30445757429573e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1775779346859017</v>
       </c>
       <c r="I18" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>8.997458515244385e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.0002205214185284594</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.0001552482862589682</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002538006262088747</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007283170720431953</v>
       </c>
       <c r="N18" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000063073627522</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.007593230376242559</v>
       </c>
       <c r="P18" t="n">
-        <v>156.1487702277424</v>
+        <v>135.6887558922882</v>
       </c>
       <c r="Q18" t="n">
-        <v>248.7833329177256</v>
+        <v>206.3835537346438</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_25_9_6</t>
+          <t>model_25_9_7</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.999912327015602</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7007661433903718</v>
       </c>
       <c r="D19" t="n">
-        <v>0.999974028462846</v>
+        <v>0.9998662637474947</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.9991481999771537</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.9996665796951589</v>
       </c>
       <c r="G19" t="n">
-        <v>0.125633654139209</v>
+        <v>5.204647081437688e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1776381435130227</v>
       </c>
       <c r="I19" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>8.493139453417711e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.0002143979742945124</v>
       </c>
       <c r="K19" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.0001496646844143448</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002561015713589572</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007214324002592126</v>
       </c>
       <c r="N19" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000061886812516</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.007521452711091938</v>
       </c>
       <c r="P19" t="n">
-        <v>156.1487702277424</v>
+        <v>135.7267471379209</v>
       </c>
       <c r="Q19" t="n">
-        <v>248.7833329177256</v>
+        <v>206.4215449802765</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_25_9_5</t>
+          <t>model_25_9_6</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9999135831974545</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.70065310314226</v>
       </c>
       <c r="D20" t="n">
-        <v>0.999974028462846</v>
+        <v>0.9998744659041874</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.9991702225785393</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.9996785556904528</v>
       </c>
       <c r="G20" t="n">
-        <v>0.125633654139209</v>
+        <v>5.130074700249696e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1777052490873864</v>
       </c>
       <c r="I20" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>7.972248077259468e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.0002088548878902579</v>
       </c>
       <c r="K20" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.0001442889363564627</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002614826376477941</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007162453979084052</v>
       </c>
       <c r="N20" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000061000095914</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.007467374473297372</v>
       </c>
       <c r="P20" t="n">
-        <v>156.1487702277424</v>
+        <v>135.7556104888828</v>
       </c>
       <c r="Q20" t="n">
-        <v>248.7833329177256</v>
+        <v>206.4504083312384</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_25_9_4</t>
+          <t>model_25_9_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9999142259709611</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.700526911085498</v>
       </c>
       <c r="D21" t="n">
-        <v>0.999974028462846</v>
+        <v>0.9998828052251568</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.9991884944845378</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.9996895777746075</v>
       </c>
       <c r="G21" t="n">
-        <v>0.125633654139209</v>
+        <v>5.091916888259789e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1777801621434933</v>
       </c>
       <c r="I21" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>7.442645859357195e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.0002042558511122342</v>
       </c>
       <c r="K21" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.0001393413770067228</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002674756499755926</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007135766874176727</v>
       </c>
       <c r="N21" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000060546373439</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.00743955124308422</v>
       </c>
       <c r="P21" t="n">
-        <v>156.1487702277424</v>
+        <v>135.7705422128622</v>
       </c>
       <c r="Q21" t="n">
-        <v>248.7833329177256</v>
+        <v>206.4653400552178</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_25_9_3</t>
+          <t>model_25_9_4</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9999140058526712</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7003860862884873</v>
       </c>
       <c r="D22" t="n">
-        <v>0.999974028462846</v>
+        <v>0.9998911286126808</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.9992011021800022</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.9996990005414885</v>
       </c>
       <c r="G22" t="n">
-        <v>0.125633654139209</v>
+        <v>5.104984060813553e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1778637618263133</v>
       </c>
       <c r="I22" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>6.914055520977195e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.0002010824955175151</v>
       </c>
       <c r="K22" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.000135111714292485</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002741667765899641</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007144917116953529</v>
       </c>
       <c r="N22" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000060701751056</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.007449091030639645</v>
       </c>
       <c r="P22" t="n">
-        <v>156.1487702277424</v>
+        <v>135.7654162712562</v>
       </c>
       <c r="Q22" t="n">
-        <v>248.7833329177256</v>
+        <v>206.4602141136118</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_25_9_2</t>
+          <t>model_25_9_3</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9999126058631165</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7002290177984656</v>
       </c>
       <c r="D23" t="n">
-        <v>0.999974028462846</v>
+        <v>0.999899220394461</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.9992055531761416</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.9997059729552972</v>
       </c>
       <c r="G23" t="n">
-        <v>0.125633654139209</v>
+        <v>5.188093488419412e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1779570044669957</v>
       </c>
       <c r="I23" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>6.400173684162556e-05</v>
       </c>
       <c r="J23" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.0001999621802671319</v>
       </c>
       <c r="K23" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.0001319819585543787</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002816293794888175</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.00720284213933598</v>
       </c>
       <c r="N23" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000061689978977</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.007509482041146244</v>
       </c>
       <c r="P23" t="n">
-        <v>156.1487702277424</v>
+        <v>135.7331183571026</v>
       </c>
       <c r="Q23" t="n">
-        <v>248.7833329177256</v>
+        <v>206.4279161994582</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_25_9_1</t>
+          <t>model_25_9_2</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9999096300313038</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.7000539457544381</v>
       </c>
       <c r="D24" t="n">
-        <v>0.999974028462846</v>
+        <v>0.9999067974582621</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.9991987072787608</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.999709413571669</v>
       </c>
       <c r="G24" t="n">
-        <v>0.125633654139209</v>
+        <v>5.364751719742544e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1780609347950489</v>
       </c>
       <c r="I24" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>5.918979854485226e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.0002016852919028412</v>
       </c>
       <c r="K24" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.0001304375452238467</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.00289960499820151</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007324446545468499</v>
       </c>
       <c r="N24" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000063790566138</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.007636263398603648</v>
       </c>
       <c r="P24" t="n">
-        <v>156.1487702277424</v>
+        <v>135.6661507354648</v>
       </c>
       <c r="Q24" t="n">
-        <v>248.7833329177256</v>
+        <v>206.3609485778204</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_25_9_11</t>
+          <t>model_25_9_1</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9999045583688728</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.6998589712925185</v>
       </c>
       <c r="D25" t="n">
-        <v>0.999974028462846</v>
+        <v>0.9999134846480264</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.9991763791575368</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.9997078840026786</v>
       </c>
       <c r="G25" t="n">
-        <v>0.125633654139209</v>
+        <v>5.665827510090394e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1781766800581026</v>
       </c>
       <c r="I25" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>5.494298930977823e-05</v>
       </c>
       <c r="J25" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.000207305277617618</v>
       </c>
       <c r="K25" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.0001311241334636982</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.002992663371785898</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007527169129287845</v>
       </c>
       <c r="N25" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000067370563149</v>
       </c>
       <c r="O25" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.007847616302509783</v>
       </c>
       <c r="P25" t="n">
-        <v>156.1487702277424</v>
+        <v>135.5569450140053</v>
       </c>
       <c r="Q25" t="n">
-        <v>248.7833329177256</v>
+        <v>206.2517428563609</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_25_9_24</t>
+          <t>model_25_9_0</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9812122674398601</v>
+        <v>0.9998967510542738</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7944647233877511</v>
+        <v>0.6996418990299987</v>
       </c>
       <c r="D26" t="n">
-        <v>0.999974028462846</v>
+        <v>0.999918807579191</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9920219881895984</v>
+        <v>0.9991333964978006</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9938783039235979</v>
+        <v>0.9996995984980122</v>
       </c>
       <c r="G26" t="n">
-        <v>0.125633654139209</v>
+        <v>6.129303430529225e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>1.374415341109035</v>
+        <v>0.1783055435301678</v>
       </c>
       <c r="I26" t="n">
-        <v>4.217870062650664e-05</v>
+        <v>5.156257481223923e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.05750392937848542</v>
+        <v>0.0002181240084582475</v>
       </c>
       <c r="K26" t="n">
-        <v>0.02877305403963102</v>
+        <v>0.0001348433054010896</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2103484809028172</v>
+        <v>0.003104891779334917</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3544483800769994</v>
+        <v>0.007828986799407203</v>
       </c>
       <c r="N26" t="n">
-        <v>1.008671261181603</v>
+        <v>1.000072881608748</v>
       </c>
       <c r="O26" t="n">
-        <v>0.3695379814261743</v>
+        <v>0.00816228297569483</v>
       </c>
       <c r="P26" t="n">
-        <v>156.1487702277424</v>
+        <v>135.3996887086903</v>
       </c>
       <c r="Q26" t="n">
-        <v>248.7833329177256</v>
+        <v>206.094486551046</v>
       </c>
     </row>
   </sheetData>
